--- a/ターゲット法人10社リスト.xlsx
+++ b/ターゲット法人10社リスト.xlsx
@@ -8,7 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="ターゲット10社リスト" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="選定基準・配点" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="候補の出し方" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="声かけスクリプト" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="選定基準・配点" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ターゲット10社リスト'!$A$3:$P$15</definedName>
@@ -20,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,8 +73,23 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <color rgb="002E3A46"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="002E3A46"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -87,6 +104,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EEF1F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0F0EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F8F9"/>
       </patternFill>
     </fill>
   </fills>
@@ -116,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -158,6 +185,39 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -593,7 +653,7 @@
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="24" customWidth="1" min="16" max="16"/>
   </cols>
@@ -608,7 +668,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>会社名を入れると『優先度スコア』『判定』が自動計算されます。選定基準・配点は右のシート参照。※社名・数値は記入例。実データに置換してください。</t>
+          <t>会社名を入れると『優先度スコア』『判定』が自動計算。候補が出ないときは『候補の出し方』シート、声のかけ方は『声かけスクリプト』シートへ。※社名・数値は記入例。実データに置換してください。</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1219,7 @@
       <formula1>"オーナー,店長,施設長・園長,エリアマネージャー,その他"</formula1>
     </dataValidation>
     <dataValidation sqref="N4:N15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力値" error="リストから選択してください" prompt="▼ から選択" type="list">
-      <formula1>"未接触,リスト化のみ,アプローチ済,返信あり,商談,初回WS実施,見送り"</formula1>
+      <formula1>"未接触,リスト化のみ,アプローチ済,返信あり,トップ受診済,商談,初回WS実施,見送り"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1167,6 +1227,602 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FFF3D6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>候補の出し方（人脈の棚卸しで10社を出す）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>選定基準⑤「紹介経由でトップに直接届く」が最も配点が高い＝自分の人脈がいちばんのリード源。下の7つの問いで候補を洗い出し、『ターゲット10社リスト』に記入してスコアで上位10社に絞る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>逆算の目安：リスト10社 → アプローチ3〜5社（M2前半）→ 初回ワークショップ1〜2社（M2・試験価格可）→ 有償受注（M3・月利20万）。10社は在庫であり、全部に声をかけるわけではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>■ 人脈の棚卸し：7つの問い（15分で書き出す）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>問い</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>出やすい業種</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>見つけた候補（メモ欄）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>この1ヶ月で客として行った店をすべて書き出す。顔見知りの店員・店長がいる店を優先</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>美容室・飲食・カフェ・サロン</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>LINE・連絡先を上から眺めて、Tier1業種（接客・飲食・宿・美容・介護・保育・式場）で働いている知人を書き出す</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>全業種</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>家族・親戚・ママ友パパ友のつながり：通っている保育園、利用中の介護施設、家族の行きつけ</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>介護・保育</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>前職・取引先のつながりで、店舗・施設ビジネスに関わる人</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>全業種</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>地元の商店会・経営者コミュニティ・マルシェ・イベントで名刺交換した人</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>飲食・小売系</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>結婚式を挙げた／最近参列した式場の担当プランナー</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>結婚式場</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>Instagram等で相互フォローの地元店舗（コールド寄りなので最後に）</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>美容・飲食</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>■ チャネル別の優先度（接点の配点と対応）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>優先</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>チャネル</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>配点</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>動き方</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>紹介（トップ直）：顔見知りのオーナー・店長</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>最優先。自分から直接「まず1回受けてみて」と言える相手。声かけスクリプトのパターンA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>紹介（担当者）：知人スタッフ経由でトップへ</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>知人に転送1本を頼む（パターンB）。知人自身にも先に受診してもらうと推進者になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>直接（コールド）・LinkedIn・イベント</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>リスト在庫として保持。M1では優先しない（Tier2と同じ扱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>■ 現場での見極めのコツ（適合サイン・除外条件の実地版）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>・店に行ったときのサイン：スタッフ同士の空気（ギスギス／よそよそしさ）、店長の疲れ顔、求人の貼り紙が出っぱなし＝痛みが顕在</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>・会話で「人が足りない」「新しい子がすぐ辞めた」が出たらメモ（離職・採用の痛み＝高）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="46" customHeight="1">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>・タイミー等のスポット人材が常時入っている店は除外（繁忙期だけの一時利用はOK。見分けは「いつ行っても知らない人がいる」か）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>・従業員3名以下は痛みも原資も弱いので見送り（リストには入れず、口コミ元として大切に）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>・トップが「うちは人を育てる」と語るか（長期雇用・育成志向＝強い のサイン）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FFF3D6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="66" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>声かけスクリプト（最初の依頼は「3分の診断を1回」だけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>提案資料1枚のCTA「まず店長・オーナーご本人が1回受けてみてください」を会話に落としたもの。売るのは刺さった後。文面はLINE想定（対面ならそのまま話す）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>■ 共通の原則</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>1. 最初のお願いは診断1回のみ（小さなYES）。ワークショップの売り込みから入らない</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>2. 相手の言葉で話す：「辞めない・回るチーム」「ギスギスが接客に出る」。研修・組織開発などの言葉は使わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>3. 受診後に「当たってる」と言った人にだけ、次の15分（デモ商談）を提案する</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>4. 断られたら深追いせず次の候補へ。リストのステータスを更新して回す</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>5. 配布URLに ?ref=社名コード を付けて、どの会社経由の受診か回答ログで識別できるようにする（下の運用メモ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>■ パターンA：顔見知りのオーナー・店長へ直接</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="96" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>文面（コピペ用）</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>◯◯さん、ちょっとお願いがあります。いま「人間関係タイプ診断」というものを作っていて、9問・3分で、力を抜いたときの自分の関わり方が8タイプで出ます。まずは◯◯さんに試しに受けてみてほしいです。
+→（診断URL）?ref=社名コード
+当たってるかどうか、率直な感想を聞かせてください。
+（刺さったら）実はこれ、お店のみんなで受けると「誰と誰がどう噛み合うか」の地図まで作れます。スタッフの定着や雰囲気づくりに使えるので、よければ15分だけ内容を説明させてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>ポイント</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>診断の面白さで入る。ワークショップの話は相手が乗ってから。「当たってる！」の一言が商談の入口。感想が薄ければ深追いしない</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>■ パターンB：知人への紹介依頼（担当者経由でトップへ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="110" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>文面（コピペ用）</t>
+        </is>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>◯◯って、たしか△△（店・施設）で働いてるよね。いま職場の人間関係を良くする仕事を始めていて、まず店長さん（オーナーさん）に3分の無料診断を受けてみてほしいんだ。よかったら下の文面をそのまま転送してもらえないかな。刺さらなかったらそれで終わりで大丈夫。
+【転送用ミニ文面】
+知人が人間関係のタイプ診断を作っています。9問3分・無料で、自然体の自分の関わり方が8タイプで出るものです。チームづくりにも使えるそうなので、よければ試してみてください。
+→（診断URL）?ref=社名コード</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>ポイント</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>紹介者の負担を最小に（転送1本で完了する文面を渡す）。紹介者自身にも先に受けてもらうと「当たる/話せる」体感で推進者になる（法人ポジショニング.md のチャンピオン）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>■ パターンC：トップ受診後のフォロー → 15分デモ商談</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="70" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>文面（コピペ用）</t>
+        </is>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>受けていただきありがとうございます。◯◯タイプ、いかがでしたか？（感想を聞く）
+もし面白いと思っていただけたら、スタッフの皆さんにも受けてもらって「チームの相性マップ」を作る90分のワークショップをやっています。開店前や休業日にできます。まず15分だけ、内容を説明させてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>ポイント</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>感想を先に聞く（的中体験を本人の言葉にしてもらう）。ステータスを「トップ受診済」に更新。15分の場で提案資料1枚を見せ、日程は仮置きまで進める</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>■ パターンD：断られたときの引き際</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>文面（コピペ用）</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>承知しました、ありがとうございます。もしスタッフの入れ替わりや雰囲気のことで困ることがあったら、いつでも声をかけてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>ポイント</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>ステータスを「見送り」にして次の候補へ。3ヶ月後に自然な接点（来店・近況）があれば再訪してよい。押した記録は残さない</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>■ URL運用メモ（?ref の挙動）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>・診断URLは（要確定：公開URL）。index.html はクエリを引き継いで prototype.html にリダイレクトする</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>・?ref=社名コード を付けると、回答ログに紹介元として記録され「どの会社経由の受診か」を識別できる（例：?ref=cafeA）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>・注意：?ref 付きは結果画面が紹介者向け（深掘り申込）表示に切り替わる仕様。検証アンケート表示のままにしたい場合は ?ref=cafeA&amp;mode=feedback と付ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>・法人文脈の結果画面出し分け（?ctx=）はM2〜M3で実装予定（文脈出し分け仕様.md）。それまでは上記で代用する</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002F8F88"/>
@@ -1191,12 +1847,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>出所：法人ポジショニング.md（1.ペルソナ／適合サイン・除外条件・選定マトリクス）</t>
+          <t>出所：法人ポジショニング.md(1.ペルソナ／適合サイン・除外条件・選定マトリクス)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>■ 適合サイン（優先して入れる）</t>
         </is>
@@ -1238,7 +1894,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>■ 除外条件（初期リストに入れない）</t>
         </is>
@@ -1259,7 +1915,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>■ 優先度スコアの見方（自動計算）</t>
         </is>
@@ -1280,36 +1936,36 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>■ 配点表（この表の数値を編集すると各行のスコアに反映されます）</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="29" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>選択肢</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="29" t="inlineStr">
         <is>
           <t>配点</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="A21" s="30" t="inlineStr">
         <is>
           <t>業種（Tier1）</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="31" t="inlineStr">
         <is>
           <t>飲食・カフェ</t>
         </is>
@@ -1319,8 +1975,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="n"/>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="A22" s="31" t="n"/>
+      <c r="B22" s="31" t="inlineStr">
         <is>
           <t>美容室・サロン</t>
         </is>
@@ -1330,8 +1986,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="n"/>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="A23" s="31" t="n"/>
+      <c r="B23" s="31" t="inlineStr">
         <is>
           <t>小規模宿</t>
         </is>
@@ -1341,8 +1997,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="n"/>
-      <c r="B24" s="20" t="inlineStr">
+      <c r="A24" s="31" t="n"/>
+      <c r="B24" s="31" t="inlineStr">
         <is>
           <t>介護・保育</t>
         </is>
@@ -1352,8 +2008,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="n"/>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="A25" s="31" t="n"/>
+      <c r="B25" s="31" t="inlineStr">
         <is>
           <t>結婚式場</t>
         </is>
@@ -1363,8 +2019,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="n"/>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="A26" s="31" t="n"/>
+      <c r="B26" s="31" t="inlineStr">
         <is>
           <t>その他Tier1</t>
         </is>
@@ -1374,8 +2030,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="n"/>
-      <c r="B27" s="20" t="inlineStr">
+      <c r="A27" s="31" t="n"/>
+      <c r="B27" s="31" t="inlineStr">
         <is>
           <t>Tier2（多店舗・宴会等）</t>
         </is>
@@ -1385,8 +2041,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="n"/>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="A28" s="31" t="n"/>
+      <c r="B28" s="31" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
@@ -1396,12 +2052,12 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="A30" s="30" t="inlineStr">
         <is>
           <t>即決度</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr">
+      <c r="B30" s="31" t="inlineStr">
         <is>
           <t>即決可（トップ即決）</t>
         </is>
@@ -1411,8 +2067,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="20" t="n"/>
-      <c r="B31" s="20" t="inlineStr">
+      <c r="A31" s="31" t="n"/>
+      <c r="B31" s="31" t="inlineStr">
         <is>
           <t>一部稟議</t>
         </is>
@@ -1422,8 +2078,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="20" t="n"/>
-      <c r="B32" s="20" t="inlineStr">
+      <c r="A32" s="31" t="n"/>
+      <c r="B32" s="31" t="inlineStr">
         <is>
           <t>稟議必要</t>
         </is>
@@ -1433,12 +2089,12 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="19" t="inlineStr">
+      <c r="A34" s="30" t="inlineStr">
         <is>
           <t>離職・採用の痛み</t>
         </is>
       </c>
-      <c r="B34" s="20" t="inlineStr">
+      <c r="B34" s="31" t="inlineStr">
         <is>
           <t>高（顕在）</t>
         </is>
@@ -1448,8 +2104,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="20" t="n"/>
-      <c r="B35" s="20" t="inlineStr">
+      <c r="A35" s="31" t="n"/>
+      <c r="B35" s="31" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -1459,8 +2115,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="20" t="n"/>
-      <c r="B36" s="20" t="inlineStr">
+      <c r="A36" s="31" t="n"/>
+      <c r="B36" s="31" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -1470,12 +2126,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="19" t="inlineStr">
+      <c r="A38" s="30" t="inlineStr">
         <is>
           <t>長期雇用・育成志向</t>
         </is>
       </c>
-      <c r="B38" s="20" t="inlineStr">
+      <c r="B38" s="31" t="inlineStr">
         <is>
           <t>強い</t>
         </is>
@@ -1485,8 +2141,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="20" t="n"/>
-      <c r="B39" s="20" t="inlineStr">
+      <c r="A39" s="31" t="n"/>
+      <c r="B39" s="31" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
@@ -1496,8 +2152,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="20" t="n"/>
-      <c r="B40" s="20" t="inlineStr">
+      <c r="A40" s="31" t="n"/>
+      <c r="B40" s="31" t="inlineStr">
         <is>
           <t>弱い</t>
         </is>
@@ -1507,8 +2163,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="20" t="n"/>
-      <c r="B41" s="20" t="inlineStr">
+      <c r="A41" s="31" t="n"/>
+      <c r="B41" s="31" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -1518,12 +2174,12 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="19" t="inlineStr">
+      <c r="A43" s="30" t="inlineStr">
         <is>
           <t>接点（経路）</t>
         </is>
       </c>
-      <c r="B43" s="20" t="inlineStr">
+      <c r="B43" s="31" t="inlineStr">
         <is>
           <t>紹介（トップ直）</t>
         </is>
@@ -1533,8 +2189,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="20" t="n"/>
-      <c r="B44" s="20" t="inlineStr">
+      <c r="A44" s="31" t="n"/>
+      <c r="B44" s="31" t="inlineStr">
         <is>
           <t>紹介（担当者）</t>
         </is>
@@ -1544,8 +2200,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="20" t="n"/>
-      <c r="B45" s="20" t="inlineStr">
+      <c r="A45" s="31" t="n"/>
+      <c r="B45" s="31" t="inlineStr">
         <is>
           <t>直接（コールド）</t>
         </is>
@@ -1555,8 +2211,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="20" t="n"/>
-      <c r="B46" s="20" t="inlineStr">
+      <c r="A46" s="31" t="n"/>
+      <c r="B46" s="31" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
@@ -1566,8 +2222,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="20" t="n"/>
-      <c r="B47" s="20" t="inlineStr">
+      <c r="A47" s="31" t="n"/>
+      <c r="B47" s="31" t="inlineStr">
         <is>
           <t>イベント・交流会</t>
         </is>
@@ -1577,8 +2233,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="20" t="n"/>
-      <c r="B48" s="20" t="inlineStr">
+      <c r="A48" s="31" t="n"/>
+      <c r="B48" s="31" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -1588,35 +2244,35 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="19" t="inlineStr">
+      <c r="A50" s="30" t="inlineStr">
         <is>
           <t>スポットワーク依存</t>
         </is>
       </c>
-      <c r="B50" s="20" t="inlineStr">
+      <c r="B50" s="31" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
       </c>
-      <c r="C50" s="20" t="n"/>
+      <c r="C50" s="31" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="20" t="n"/>
-      <c r="B51" s="20" t="inlineStr">
+      <c r="A51" s="31" t="n"/>
+      <c r="B51" s="31" t="inlineStr">
         <is>
           <t>一時的のみ</t>
         </is>
       </c>
-      <c r="C51" s="20" t="n"/>
+      <c r="C51" s="31" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="20" t="n"/>
-      <c r="B52" s="20" t="inlineStr">
+      <c r="A52" s="31" t="n"/>
+      <c r="B52" s="31" t="inlineStr">
         <is>
           <t>恒常依存（除外）</t>
         </is>
       </c>
-      <c r="C52" s="20" t="n"/>
+      <c r="C52" s="31" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
